--- a/data/trans_orig/IP2905_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2905_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47426</t>
+          <t>46780</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63718</t>
+          <t>64069</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63256</t>
+          <t>63123</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86719</t>
+          <t>86262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115474</t>
+          <t>117919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145273</t>
+          <t>144618</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36422</t>
+          <t>36071</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52714</t>
+          <t>53360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45947</t>
+          <t>46404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69410</t>
+          <t>69543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87533</t>
+          <t>88188</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117332</t>
+          <t>114887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37545</t>
+          <t>36918</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54869</t>
+          <t>53020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36930</t>
+          <t>36511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53269</t>
+          <t>53366</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79849</t>
+          <t>79067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102596</t>
+          <t>102997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38523</t>
+          <t>40372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55847</t>
+          <t>56474</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39975</t>
+          <t>39878</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56314</t>
+          <t>56733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84041</t>
+          <t>83640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106788</t>
+          <t>107570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>17865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>29460</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24975</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39274</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47186</t>
+          <t>46659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64661</t>
+          <t>65784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>59,38%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>30584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23060</t>
+          <t>22177</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37359</t>
+          <t>37793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46122</t>
+          <t>44999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63597</t>
+          <t>64124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,88%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78768</t>
+          <t>77505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104816</t>
+          <t>104813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90743</t>
+          <t>91478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120495</t>
+          <t>120483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176136</t>
+          <t>177618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215318</t>
+          <t>217745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80744</t>
+          <t>80747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106792</t>
+          <t>108055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90411</t>
+          <t>90423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120163</t>
+          <t>119428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>181148</t>
+          <t>178721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>220330</t>
+          <t>218848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49507</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69576</t>
+          <t>68914</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71124</t>
+          <t>70619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101634</t>
+          <t>100238</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128147</t>
+          <t>126555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163022</t>
+          <t>161701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46055</t>
+          <t>46717</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66124</t>
+          <t>65208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57827</t>
+          <t>59223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88337</t>
+          <t>88842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112070</t>
+          <t>113391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146945</t>
+          <t>148537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35915</t>
+          <t>36210</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32436</t>
+          <t>32295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44152</t>
+          <t>42623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63564</t>
+          <t>64336</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31475</t>
+          <t>31180</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45967</t>
+          <t>45337</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35632</t>
+          <t>35773</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50049</t>
+          <t>49975</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71894</t>
+          <t>71122</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91306</t>
+          <t>92835</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>282589</t>
+          <t>282769</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>328435</t>
+          <t>326168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>340051</t>
+          <t>341116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>394512</t>
+          <t>398563</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>634102</t>
+          <t>634097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>707447</t>
+          <t>705620</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>282127</t>
+          <t>284394</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>327973</t>
+          <t>327793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>332167</t>
+          <t>328116</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>386628</t>
+          <t>385563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>629794</t>
+          <t>631621</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>703139</t>
+          <t>703144</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/IP2905_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2905_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69809</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>59361</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>79184</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>49,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66,66%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>55340</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46780</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>64069</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>76012</t>
+          <t>54162</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63123</t>
+          <t>45508</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86262</t>
+          <t>62540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>131352</t>
+          <t>123971</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117919</t>
+          <t>111427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144618</t>
+          <t>136338</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48981</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39606</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>59429</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,34%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>44800</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36071</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53360</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>44,74%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53,29%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56654</t>
+          <t>44603</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46404</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69543</t>
+          <t>53257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>101454</t>
+          <t>93583</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88188</t>
+          <t>81216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114887</t>
+          <t>106127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118790</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118790</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118790</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>100140</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>100140</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>100140</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>98765</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>98765</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>98765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>232806</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232806</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>232806</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43924</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35540</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>51733</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>49,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>39,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>45495</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36918</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>53020</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>48,71%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>39,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>56,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>46781</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36511</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53366</t>
+          <t>54797</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>90725</t>
+          <t>90706</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79067</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102997</t>
+          <t>102900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,66%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45549</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37740</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>53933</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>50,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>60,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>47897</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40372</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56474</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>51,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>43,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>48014</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39878</t>
+          <t>40613</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56733</t>
+          <t>56707</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>95912</t>
+          <t>94177</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83640</t>
+          <t>81983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107570</t>
+          <t>105734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89473</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89473</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89473</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>186637</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>186637</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>186637</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27798</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21505</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33900</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>23583</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17865</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29460</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>48,68%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>36,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24541</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>55803</t>
+          <t>51004</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46659</t>
+          <t>42196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65784</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28046</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>21944</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34339</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>61,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>24866</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18989</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30584</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>51,32%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>63,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30114</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>20109</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37793</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>54980</t>
+          <t>54571</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44999</t>
+          <t>45657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64124</t>
+          <t>63379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>48449</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>48449</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48449</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>110783</t>
+          <t>105575</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110783</t>
+          <t>105575</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110783</t>
+          <t>105575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>98662</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>85510</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>113301</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>50,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>57,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>91071</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>77505</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>104813</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>49,08%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>105705</t>
+          <t>81141</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91478</t>
+          <t>70347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120483</t>
+          <t>91884</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>196776</t>
+          <t>179802</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177618</t>
+          <t>163093</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>217745</t>
+          <t>198515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>96947</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>82308</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>110099</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>49,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>42,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>94489</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>80747</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>108055</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>50,92%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>58,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>105201</t>
+          <t>89481</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90423</t>
+          <t>78738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119428</t>
+          <t>100275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>199690</t>
+          <t>186429</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178721</t>
+          <t>167716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218848</t>
+          <t>203138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>195609</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>195609</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>195609</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>185560</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>185560</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>185560</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>170622</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>170622</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>170622</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>396466</t>
+          <t>366231</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>396466</t>
+          <t>366231</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>396466</t>
+          <t>366231</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>74319</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>62792</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>89444</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,05%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>61,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>60071</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>50423</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68914</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>51,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>43,61%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>59,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>84339</t>
+          <t>62711</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70619</t>
+          <t>53110</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100238</t>
+          <t>71463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>144410</t>
+          <t>137030</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126555</t>
+          <t>120847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161701</t>
+          <t>154490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>71267</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>56142</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>82794</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>48,95%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>38,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>55560</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>46717</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>65208</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>48,05%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>40,4%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>56,39%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>75122</t>
+          <t>52799</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59223</t>
+          <t>44047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88842</t>
+          <t>62400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>130682</t>
+          <t>124066</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113391</t>
+          <t>106606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148537</t>
+          <t>140249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,72%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115631</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115631</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115631</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115510</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115510</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115510</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>275092</t>
+          <t>261096</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>275092</t>
+          <t>261096</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>275092</t>
+          <t>261096</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>21430</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>15099</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>28558</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>33,02%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>23,26%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>28912</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>22053</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>36210</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>42,9%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>53,73%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24618</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18093</t>
+          <t>20558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>35976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>53530</t>
+          <t>49864</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>40438</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64336</t>
+          <t>60172</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>43480</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>36352</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>49811</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>66,98%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>56,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>76,74%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>38478</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>31180</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>45337</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>57,1%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>46,27%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>67,28%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43450</t>
+          <t>40329</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35773</t>
+          <t>32787</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49975</t>
+          <t>48205</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>81928</t>
+          <t>83809</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>73501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92835</t>
+          <t>93235</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64910</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64910</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64910</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>67390</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>67390</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>67390</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>68763</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>68763</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>68763</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>135458</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>135458</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135458</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>335943</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>311500</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>362701</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>50,12%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>46,48%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>54,12%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>304473</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>282769</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>326168</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>49,87%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>46,31%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>53,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>368123</t>
+          <t>296435</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>341116</t>
+          <t>276968</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>398563</t>
+          <t>316223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>672595</t>
+          <t>632379</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>634097</t>
+          <t>600035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>705620</t>
+          <t>663607</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>334269</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>307511</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>358712</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>49,88%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>45,88%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>53,52%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>449</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>306089</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>284394</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>327793</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>50,13%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>46,58%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>53,69%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>358556</t>
+          <t>302366</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>328116</t>
+          <t>282578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>321833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>664646</t>
+          <t>636634</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>631621</t>
+          <t>605406</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>703144</t>
+          <t>668978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>670212</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>670212</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>670212</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>893</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>610562</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>610562</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>610562</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>915</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>726679</t>
+          <t>598801</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>726679</t>
+          <t>598801</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>726679</t>
+          <t>598801</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1337241</t>
+          <t>1269013</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1337241</t>
+          <t>1269013</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1337241</t>
+          <t>1269013</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
